--- a/paper_info_0018.xlsx
+++ b/paper_info_0018.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Fang et al. (2022) — see source_artifacts/Paper_AntiCorruption/</t>
+          <t>Fang, Y., Kong, G., Nofsinger, J. R., &amp; Wang, M.</t>
         </is>
       </c>
     </row>
